--- a/LoanOfficer-A/2023/52 bimola.xlsx
+++ b/LoanOfficer-A/2023/52 bimola.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4500</v>
+        <v>6200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7500</v>
+        <v>5800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45579</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -913,9 +919,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45581</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -1433,9 +1445,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45563</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1465,9 +1483,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45564</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1497,9 +1521,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45565</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1529,9 +1559,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45566</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1561,9 +1597,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45568</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1593,9 +1635,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1625,9 +1673,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45569</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1657,9 +1711,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45570</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1689,9 +1749,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45571</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1721,9 +1787,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45572</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1753,9 +1825,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45573</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1785,9 +1863,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45574</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1817,9 +1901,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45575</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1849,9 +1939,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45577</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1881,9 +1977,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45579</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>
